--- a/apps/web/public/plantilla-sitios-set.xlsx
+++ b/apps/web/public/plantilla-sitios-set.xlsx
@@ -578,7 +578,7 @@
         <v>Cómo se comercializa. REGLA: si exhibicion=fijo solo "mensual" o "catorcenal".</v>
       </c>
       <c r="D27" t="str">
-        <v>mensual · catorcenal · semanal · diaria · spot · hora · programatico</v>
+        <v>mensual · catorcenal · semanal · diaria · spot (CPS, costo por salida) · hora · programatico · cpm (costo por millar)</v>
       </c>
     </row>
     <row r="28">
@@ -1241,7 +1241,7 @@
         <v/>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>cpm</v>
       </c>
       <c r="C9" t="str">
         <v/>
